--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564064351</v>
+        <v>46157.93083241819</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93083241819</v>
+        <v>46157.93161761834</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93161761834</v>
+        <v>46157.93396152688</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396152688</v>
+        <v>46157.93713350403</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713350403</v>
+        <v>46158.28212651035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212651035</v>
+        <v>46158.29673827002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673827002</v>
+        <v>46158.29809838911</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809838911</v>
+        <v>46158.33383483307</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383483307</v>
+        <v>46158.36851849048</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/21. Статус-2 (Мира, 59)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36851849048</v>
+        <v>46158.37283678774</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
